--- a/metadata/gongfa/catalog.xlsx
+++ b/metadata/gongfa/catalog.xlsx
@@ -485,7 +485,7 @@
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>合计410条；原登记库 79；此前四HTML 211；Solve已审首24 24；HTML续提 96；输入：f78e799ed13956b958831310efb201cfd7b2339d6863e40b02139211bba7faf2</t>
+          <t>合计410条；原登记库 79；此前四HTML 211；Solve已审首24 24；HTML续提 96；输入：07ed857bb608571059c2a4b90695d99143bb657b5e9971a6351a97b548ba9a66</t>
         </is>
       </c>
     </row>
@@ -594,35 +594,164 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>天高</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>拼好码</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>复合（保留上位）</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>已登记</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>原登记库</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>复用主导的软件系统组装与演化</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>#vibecoding方法论 ，“拼好码”是一种复用主导的软件工程范式，用于在既有能力空间中完成需求匹配、方案选择与业务编排，以奖励搜索、组装能力，并且惩罚自研、强调以低自研成本获得可验证、可替换、可回滚的系统。其机制为“需求→候选能力→选择→适配→编排→检验→更新”：成熟组件承担通用复杂度，薄胶水表达领域差异，测试与CI提供经验检验。其成立依赖方案可识别、维护稳定、接口可隔离；若供应链不可观测、依赖锁定或关键约束超出现有能力，复用可能转化为系统性风险。方法上需以偏离说明、替换路径和回滚机制闭环，并据运行结果更新方案。该范式关联模块化、组件复用、软件供应链与AI辅助开发。其核心问题是：如何在既有能力构成的假设空间中，以合理归纳偏置平衡复用效率、业务差异与长期演化。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>选区说明：只取标题下的方法段落；页面根节点和宏观表述不构成本体继承、权限授予或品级证据。
+条件：[
+  "方案可识别、维护稳定、接口可隔离。"
+]
+限制：[
+  "供应链不可观测、依赖锁定或关键约束超出现有能力时，复用可能转化为系统性风险。"
+]</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>用户要求将拼好码提升至天阶上品，按项目词表映射为天阶高级（tian-advanced）。与组块理论的关联作为结构类比：把成熟能力组织为可识别、可复用、可组合的单元，再由拼好码完成需求匹配、边界适配和编排，可能使复杂问题的处理转向更高层次的系统组合与业务表达。该机制假设支持用户指定的最高档暂定判断，但并非受控任务结果，尚未证明相对固定合理基线突破了明确能力缺口。</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>若预先固定的组块化软件组合任务中，相比合理基线未达到预定正确性、可靠性、成本与可维护性阈值，或组件边界/接口错配、供应链与依赖风险抵消收益，则应下调；若组块化并未带来可重复的高层组合优势，该机制假设亦被推翻。</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>gongfa-glue-coding</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>{
+  "source": {
+    "id": "tradecatlabs-vibe-coding-methodology-page",
+    "kind": "project_internal_publication",
+    "url": "https://tradecatlabs.com/portfolio/02-vibe-coding-cn/",
+    "resolved_url": "https://tradecatlabs.com/portfolio/02-vibe-coding-cn/",
+    "captured_at": "2026-10-07T04:17:07.958661Z",
+    "snapshot_path": "metadata/gongfa/source-methodology-931f79be.txt",
+    "snapshot_sha256": "931f79be42fee9c17a2765214977b5c30311fbbd0ab983f510fefff784705de2",
+    "text_normalization": "html-text-whitespace-v1",
+    "included_anchors": [
+      "固定点收敛系统",
+      "递归式-ai-治理",
+      "拼好码",
+      "吸引子",
+      "有限样本生成推断",
+      "ai-native",
+      "拍扁",
+      "符号序列空间与有效知识子集",
+      "合成模型",
+      "解空间",
+      "近端因果机制",
+      "目的导向的行动选择",
+      "预测加工与模型更新",
+      "受约束的状态变换",
+      "最小先验条件下的代理增强型任务求解",
+      "projection-表示转换",
+      "状态分类工具"
+    ]
+  },
+  "selection": {
+    "source_id": "tradecatlabs-vibe-coding-methodology-page",
+    "heading_id": "拼好码",
+    "selection": "html-paragraph",
+    "stop_before": null
+  },
+  "original_proposal_context": "[\n  {\n    \"batch_id\": \"gongfa-author-initial-20261007\",\n    \"application_context\": \"在中文软件工程知识库中选择并应用功法：以各条task_family中的判断、设计、排错或受控交付为目标，先要求正确性、安全、权限和可验收性，再考虑效果、可靠性与成本；所需观测、技能和验证能力需另行满足。任务集、环境、预算与阈值尚未实验冻结。\",\n    \"baseline_assumption\": \"假定对照采用胜任的现行需求、设计、实现和相关验证流程，在相同目标、信息、环境及预算下比较；不故意选择不测试、忽略安全或能力不足的弱基线。若基线已完整采用同一方法，则不得据初评推定额外增益。此处是前瞻假设，不是已运行基线。\",\n    \"assessed_at\": \"2026-10-07T07:47:52.872364Z\",\n    \"item\": {\n      \"gongfa_id\": \"gongfa-glue-coding\",\n      \"content_version\": \"r1\",\n      \"content_sha256\": \"7ee9dc827a5bceca480aa7d2b969cfd49a097b4791acb970c7e47ede82393c9c\",\n      \"ontology_type\": \"dao-content\",\n      \"grade_id\": \"tian-advanced\",\n      \"task_family\": \"复用主导的软件系统组装与演化\",\n      \"classification_reason\": \"条目把复用价值准则、工程机制及需求到验证的流程作为完整范式表达。\",\n      \"reason\": \"用户要求将拼好码提升至天阶上品，按项目词表映射为天阶高级（tian-advanced）。与组块理论的关联作为结构类比：把成熟能力组织为可识别、可复用、可组合的单元，再由拼好码完成需求匹配、边界适配和编排，可能使复杂问题的处理转向更高层次的系统组合与业务表达。该机制假设支持用户指定的最高档暂定判断，但并非受控任务结果，尚未证明相对固定合理基线突破了明确能力缺口。\",\n      \"confidence\": \"low\",\n      \"falsifier\": \"若预先固定的组块化软件组合任务中，相比合理基线未达到预定正确性、可靠性、成本与可维护性阈值，或组件边界/接口错配、供应链与依赖风险抵消收益，则应下调；若组块化并未带来可重复的高层组合优势，该机制假设亦被推翻。\"\n    }\n  }\n]"
+}</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>7ee9dc827a5bceca480aa7d2b969cfd49a097b4791acb970c7e47ede82393c9c</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T07:47:52.872364Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>地高</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>第一性原理</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>错误前提下的问题重构与方案重推</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>把问题拆到不能再依赖既有说法、行业惯例和二手结论的基础事实，再从基础事实重新推导方案。
 适合：
@@ -638,7 +767,7 @@
 在 Vibe Coding 中，它常用于防止 AI 沿着常见套路生成过度复杂方案。</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>选区说明：收录当前仓内五步操作版，不宣称覆盖第一性原理的全部历史表述。
 条件：[
@@ -646,32 +775,32 @@
 ]</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>预计在需求含错误假设的困难或迁移任务中纠正问题定义并重建可行方案；不是通用最优解保证。</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>若不能识别错误前提，重推方案违反事实或预算，或成熟基线已经同样处理这些前提，应下调。</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>gongfa-first-principles</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -703,53 +832,53 @@
 }</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>e92e76bdb2c16e50f9303929b3383074564aaa4b4728859b3deba3750790e71a</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>地高</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>形式化方法（轻量形式化）</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>协议、不变量与边界条件检查</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>**用途**：减少非法状态、约束模型输出、让行为可检查可累积。
 **落地动作**：
@@ -768,37 +897,37 @@
 ```</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收编号方法节的用途、操作、工具建议与提示词；数字建议和工具名称不自动成为倍率、唯一依赖或授权。</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>预计在复杂协议与边界案例中发现常规示例测试遗漏的不一致；结论受模型和工具保证范围限制。</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>若形式模型遗漏用户关键性质、验证方向错误，或工具通过却实际契约违约，应下调。</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>gongfa-lightweight-formal-methods</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -848,53 +977,53 @@
 }</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>bee84e77c89b64a2aefb1f6fff50c9c181028905364860b295356f1f4d47c13c</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>地高</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>方法论工具箱总体作业流</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>从需求澄清到交付验证的整体作业</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>建议默认流程：
 1. **现象卡片**（现象/意图/情境/边界）→ 清零脑补
@@ -905,37 +1034,37 @@
 6. **收敛重构**（删复杂度、固化概念、稳定接口、补文档）→ 可维护</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收六步总体作业流，不合并下方23个独立方法或工具配置。</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>预计在复杂交付与迁移任务中减少阶段脱节和无验收实现，形成目标与结果的可核对链。</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>若前后阶段的条件和证据不一致、实现未被独立验收，或额外流程成本超过任务预算，应下调。</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>gongfa-methodology-delivery-loop</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -985,53 +1114,53 @@
 }</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>6f224bc1df90eee7f2d857e492b3465a1d04801e579b7f8f20e592758c1ca5c6</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>地中</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>胶水原则</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>准则型</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>技术选型与成熟能力复用</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>“胶水原则”是最高级别的“不重复造轮子”：能复用成熟方案就不自研底层能力，只写用于连接、编排、适配、隔离和表达业务逻辑的胶水代码。
 默认答案不是“我来实现”，而是：
@@ -1039,7 +1168,7 @@
 当成熟方案能以可接受的成本、风险和复杂度可靠满足需求时，它就是默认答案；自研不是默认选项，而是需要证明合理性的例外选项。</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收成熟能力优先准则及自研例外，不收整篇拼好码交付流程。
 条件：[
@@ -1050,32 +1179,32 @@
 ]</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>预计在陌生技术和维护约束较强的任务中减少自研错误与长期所有权成本，但复用必须满足关键约束。</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>若依赖无法维护、集成成本超过收益、供应链风险失控，或关键约束不满足，初评应下调。</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>gongfa-glue-principle</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -1101,53 +1230,53 @@
 }</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>e761c7f0a020ec6e5fd12ebfa2496fc869f7dd29a982fc849a9c0b849d8ef44f</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>地中</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>反事实推理（Counterfactuals）</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>因果解释与验证器的反事实检查</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>**用途**：系统性覆盖异常路径，降低线上事故。
 **落地动作**：
@@ -1160,37 +1289,37 @@
 ```</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收编号方法节的用途、操作、工具建议与提示词；数字建议和工具名称不自动成为倍率、唯一依赖或授权。</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>预计能在困难排错与迁移验证中暴露自证、混杂和不敏感测试；反事实必须可比较。</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>若改变多个混杂因素、预期值复写实现，或测试对已知缺陷仍不敏感，应下调。</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>gongfa-counterfactual-testing</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -1240,53 +1369,53 @@
 }</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>e57e942bf45b08954531e3b0be0e11580237d5017f773e5c024b7d1b4b03dce0</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>地中</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>溯因排错法（仓内操作版）</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>多候选原因的故障诊断</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>**用途**：debug/性能退化时，比穷举更快定位"最可能原因"。
 **落地动作**：
@@ -1299,7 +1428,7 @@
 ```</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收编号方法节的用途、操作、工具建议与提示词；数字建议和工具名称不自动成为倍率、唯一依赖或授权。
 条件：[
@@ -1307,32 +1436,32 @@
 ]</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>预计在多原因且成本受限的故障中减少盲改和无信息重试，较单假设调试更易保留替代解释。</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>若候选集遗漏真实原因、实验无法区分假设，或观察失败却不更新解释，应下调。</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>gongfa-abductive-debugging</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -1382,53 +1511,53 @@
 }</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>a9b821e8da4740b609d4252e935dbd7859e9393663e922c5a0ed6904be03682b</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>地中</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>错误认识论（Error epistemology）</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>高风险方案的失败模式与防护分析</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>**用途**：系统化"我们会如何错"，比事后补洞更省。
 **落地动作**：
@@ -1441,37 +1570,37 @@
 ```</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收编号方法节的用途、操作、工具建议与提示词；数字建议和工具名称不自动成为倍率、唯一依赖或授权。</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>预计在困难场景中提高对部分失败和恢复路径的覆盖；清单本身不证明防护有效。</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>若主要故障模式仍遗漏、错误检测不敏感，或恢复措施在受控故障中不能执行，应下调。</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>gongfa-failure-mode-analysis</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -1521,53 +1650,53 @@
 }</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>9245e35da05e68b72a9a0519b46919e4ef10c263b29e40f549d9c8421b9a1cbc</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>地中</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>实验哲学（x-phi）</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>可区分假设的工程实验设计</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>**用途**：交互与默认策略别靠直觉，用数据决定。
 **落地动作**：
@@ -1580,7 +1709,7 @@
 ```</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>选区说明：只收编号方法节的用途、操作、工具建议与提示词；数字建议和工具名称不自动成为倍率、唯一依赖或授权。
 条件：[
@@ -1588,32 +1717,32 @@
 ]</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>预计能在多因素问题中减少混杂和错误归因，支持困难假设的淘汰；外推范围仍受样本限制。</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>若对照不可比、变量控制失败、oracle不独立，或实验不足以区分候选假设，应下调。</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>gongfa-experimental-design</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -1663,58 +1792,58 @@
 }</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>f06a372c255f5363d8555a0e30999ea6c6c0904d432dcaca20491b168af856e1</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2026-10-07T07:47:52.872364Z</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>地中</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>固定点收敛系统</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>方法型</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>已登记</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>原登记库</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>自治任务执行的分层验证与升级</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>#vibecoding方法论 ，固定点收敛系统可界定为自主智能体的分层闭环控制框架，用于将意图转化为可执行、可验证且受变更约束的目标状态，并持续缩小现实与目标的偏差。其机制遵循“观察→差距识别→行动→验证→修正”，行动失效则升级策略，策略失效则复审目标，目标不可确定时回退需求或交由人工裁决。该框架依赖目标可识别、状态可观测、验证准则一致及策略空间中存在有效控制路径；缺乏稳定性或充分反馈时，“收敛”只能作为架构期望。方法上形成“需求澄清→目标冻结→计划→执行→验证→更新→升级”的闭环，并与需求工程、反馈控制、自治计算、监督控制及运行时保障相衔接。其核心问题是：动态环境下，如何以分层约束获得对目标趋近过程的可验证控制。</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>选区说明：只取标题下的方法段落；页面根节点和宏观表述不构成本体继承、权限授予或品级证据。
 条件：[
@@ -1725,32 +1854,32 @@
 ]</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>预计在动态或执行反复失效的任务中更好地区分行动、策略和目标问题，保留人工退出；不预言数学收敛。</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>若目标不可识别、验证信号不可靠、升级持续振荡或无法退出，初评应下调。</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>gongfa-fixed-point-convergence</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>r1</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>{
   "source": {
@@ -1792,138 +1921,9 @@
 }</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>228dc7de506eceac46c6f19d9c679c39e43f581991c9c3caae93d021d3d0823a</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T07:47:52.872364Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>地中</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>拼好码</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>复合（保留上位）</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>已登记</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>原登记库</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>复用主导的软件系统组装与演化</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>#vibecoding方法论 ，“拼好码”是一种复用主导的软件工程范式，用于在既有能力空间中完成需求匹配、方案选择与业务编排，以奖励搜索、组装能力，并且惩罚自研、强调以低自研成本获得可验证、可替换、可回滚的系统。其机制为“需求→候选能力→选择→适配→编排→检验→更新”：成熟组件承担通用复杂度，薄胶水表达领域差异，测试与CI提供经验检验。其成立依赖方案可识别、维护稳定、接口可隔离；若供应链不可观测、依赖锁定或关键约束超出现有能力，复用可能转化为系统性风险。方法上需以偏离说明、替换路径和回滚机制闭环，并据运行结果更新方案。该范式关联模块化、组件复用、软件供应链与AI辅助开发。其核心问题是：如何在既有能力构成的假设空间中，以合理归纳偏置平衡复用效率、业务差异与长期演化。</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>选区说明：只取标题下的方法段落；页面根节点和宏观表述不构成本体继承、权限授予或品级证据。
-条件：[
-  "方案可识别、维护稳定、接口可隔离。"
-]
-限制：[
-  "供应链不可观测、依赖锁定或关键约束超出现有能力时，复用可能转化为系统性风险。"
-]</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>预计在陌生领域和维护要求较高的任务中减少重复自研并保留替换回滚；并非复用越多越强。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>若供应链或依赖锁定风险不可控、接口无法隔离，或关键约束超出候选能力，应下调。</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>gongfa-glue-coding</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>r1</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>{
-  "source": {
-    "id": "tradecatlabs-vibe-coding-methodology-page",
-    "kind": "project_internal_publication",
-    "url": "https://tradecatlabs.com/portfolio/02-vibe-coding-cn/",
-    "resolved_url": "https://tradecatlabs.com/portfolio/02-vibe-coding-cn/",
-    "captured_at": "2026-10-07T04:17:07.958661Z",
-    "snapshot_path": "metadata/gongfa/source-methodology-931f79be.txt",
-    "snapshot_sha256": "931f79be42fee9c17a2765214977b5c30311fbbd0ab983f510fefff784705de2",
-    "text_normalization": "html-text-whitespace-v1",
-    "included_anchors": [
-      "固定点收敛系统",
-      "递归式-ai-治理",
-      "拼好码",
-      "吸引子",
-      "有限样本生成推断",
-      "ai-native",
-      "拍扁",
-      "符号序列空间与有效知识子集",
-      "合成模型",
-      "解空间",
-      "近端因果机制",
-      "目的导向的行动选择",
-      "预测加工与模型更新",
-      "受约束的状态变换",
-      "最小先验条件下的代理增强型任务求解",
-      "projection-表示转换",
-      "状态分类工具"
-    ]
-  },
-  "selection": {
-    "source_id": "tradecatlabs-vibe-coding-methodology-page",
-    "heading_id": "拼好码",
-    "selection": "html-paragraph",
-    "stop_before": null
-  },
-  "original_proposal_context": "[\n  {\n    \"batch_id\": \"gongfa-author-initial-20261007\",\n    \"application_context\": \"在中文软件工程知识库中选择并应用功法：以各条task_family中的判断、设计、排错或受控交付为目标，先要求正确性、安全、权限和可验收性，再考虑效果、可靠性与成本；所需观测、技能和验证能力需另行满足。任务集、环境、预算与阈值尚未实验冻结。\",\n    \"baseline_assumption\": \"假定对照采用胜任的现行需求、设计、实现和相关验证流程，在相同目标、信息、环境及预算下比较；不故意选择不测试、忽略安全或能力不足的弱基线。若基线已完整采用同一方法，则不得据初评推定额外增益。此处是前瞻假设，不是已运行基线。\",\n    \"assessed_at\": \"2026-10-07T07:47:52.872364Z\",\n    \"item\": {\n      \"gongfa_id\": \"gongfa-glue-coding\",\n      \"content_version\": \"r1\",\n      \"content_sha256\": \"7ee9dc827a5bceca480aa7d2b969cfd49a097b4791acb970c7e47ede82393c9c\",\n      \"ontology_type\": \"dao-content\",\n      \"grade_id\": \"di-intermediate\",\n      \"task_family\": \"复用主导的软件系统组装与演化\",\n      \"classification_reason\": \"条目把复用价值准则、工程机制及需求到验证的流程作为完整范式表达。\",\n      \"reason\": \"预计在陌生领域和维护要求较高的任务中减少重复自研并保留替换回滚；并非复用越多越强。\",\n      \"confidence\": \"medium\",\n      \"falsifier\": \"若供应链或依赖锁定风险不可控、接口无法隔离，或关键约束超出候选能力，应下调。\"\n    }\n  }\n]"
-}</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>7ee9dc827a5bceca480aa7d2b969cfd49a097b4791acb970c7e47ede82393c9c</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>

--- a/metadata/gongfa/catalog.xlsx
+++ b/metadata/gongfa/catalog.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>天高</t>
+          <t>天阶高级</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>地高</t>
+          <t>地阶高级</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>地高</t>
+          <t>地阶高级</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>地高</t>
+          <t>地阶高级</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>地中</t>
+          <t>地阶中级</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>地初</t>
+          <t>地阶初级</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -13663,7 +13663,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -13887,7 +13887,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -13999,7 +13999,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -16817,7 +16817,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -17155,7 +17155,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -18363,7 +18363,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -18472,7 +18472,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -18793,7 +18793,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -19025,7 +19025,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -19135,7 +19135,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -19700,7 +19700,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -20418,7 +20418,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -20654,7 +20654,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -21570,7 +21570,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -21683,7 +21683,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -22140,7 +22140,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -22253,7 +22253,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -22602,7 +22602,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -22833,7 +22833,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -23059,7 +23059,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -23295,7 +23295,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -23409,7 +23409,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -23631,7 +23631,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -23745,7 +23745,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -24086,7 +24086,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -24199,7 +24199,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -24425,7 +24425,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -24538,7 +24538,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -24763,7 +24763,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -25107,7 +25107,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -25220,7 +25220,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -25451,7 +25451,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -25677,7 +25677,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -25795,7 +25795,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -26026,7 +26026,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -26257,7 +26257,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -26482,7 +26482,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -27505,7 +27505,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -28211,7 +28211,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -28572,7 +28572,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>玄高</t>
+          <t>玄阶高级</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -29017,7 +29017,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -29145,7 +29145,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -29428,7 +29428,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -29570,7 +29570,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -29854,7 +29854,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -29995,7 +29995,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -30253,7 +30253,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -30511,7 +30511,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -30640,7 +30640,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -30768,7 +30768,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -31279,7 +31279,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -31506,7 +31506,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -31618,7 +31618,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -31730,7 +31730,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -31954,7 +31954,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -32070,7 +32070,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -32182,7 +32182,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -32294,7 +32294,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -32406,7 +32406,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -32518,7 +32518,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -32630,7 +32630,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -32742,7 +32742,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -32854,7 +32854,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -32966,7 +32966,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -33078,7 +33078,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -33190,7 +33190,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -33302,7 +33302,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -33414,7 +33414,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -33526,7 +33526,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -33638,7 +33638,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -33862,7 +33862,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -34088,7 +34088,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -34200,7 +34200,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -34312,7 +34312,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -34424,7 +34424,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -34536,7 +34536,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -34760,7 +34760,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -34872,7 +34872,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -34984,7 +34984,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -35102,7 +35102,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -35214,7 +35214,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
@@ -35326,7 +35326,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -35433,7 +35433,7 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
@@ -35540,7 +35540,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -35647,7 +35647,7 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
@@ -35758,7 +35758,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -35865,7 +35865,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
@@ -35976,7 +35976,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -36083,7 +36083,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
@@ -36190,7 +36190,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -36297,7 +36297,7 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
@@ -36404,7 +36404,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -36514,7 +36514,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -36728,7 +36728,7 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
@@ -36835,7 +36835,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -36945,7 +36945,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
@@ -37165,7 +37165,7 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -37385,7 +37385,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -37495,7 +37495,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -37605,7 +37605,7 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
@@ -38162,7 +38162,7 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -38272,7 +38272,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -38382,7 +38382,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -38492,7 +38492,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
@@ -38611,7 +38611,7 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -38721,7 +38721,7 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -38834,7 +38834,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
@@ -39060,7 +39060,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -39286,7 +39286,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -39393,7 +39393,7 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -39500,7 +39500,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -39618,7 +39618,7 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -39731,7 +39731,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -39839,7 +39839,7 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -39953,7 +39953,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -40186,7 +40186,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -40300,7 +40300,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -40414,7 +40414,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -40522,7 +40522,7 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -40629,7 +40629,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -40855,7 +40855,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -40962,7 +40962,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -41080,7 +41080,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -41193,7 +41193,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -41650,7 +41650,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -41757,7 +41757,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -41870,7 +41870,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -41983,7 +41983,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -42096,7 +42096,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -42209,7 +42209,7 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -42322,7 +42322,7 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -42434,7 +42434,7 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -42620,7 +42620,7 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>玄中</t>
+          <t>玄阶中级</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -42807,7 +42807,7 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -42946,7 +42946,7 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -43085,7 +43085,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -43214,7 +43214,7 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
@@ -43343,7 +43343,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -43469,7 +43469,7 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -43693,7 +43693,7 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -43917,7 +43917,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
@@ -44029,7 +44029,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -44136,7 +44136,7 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
@@ -44250,7 +44250,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -44361,7 +44361,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
@@ -44468,7 +44468,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -44575,7 +44575,7 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
@@ -44682,7 +44682,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -44793,7 +44793,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -45007,7 +45007,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
@@ -45114,7 +45114,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -45221,7 +45221,7 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
@@ -45335,7 +45335,7 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -45445,7 +45445,7 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
@@ -45555,7 +45555,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -45893,7 +45893,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
@@ -46007,7 +46007,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -46121,7 +46121,7 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
@@ -46234,7 +46234,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -46341,7 +46341,7 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
@@ -46448,7 +46448,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -46561,7 +46561,7 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
@@ -46674,7 +46674,7 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -46787,7 +46787,7 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
@@ -46900,7 +46900,7 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -47013,7 +47013,7 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>玄初</t>
+          <t>玄阶初级</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
@@ -47126,7 +47126,7 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -47239,7 +47239,7 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
@@ -47379,7 +47379,7 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
@@ -47509,7 +47509,7 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
@@ -47638,7 +47638,7 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -47761,7 +47761,7 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
@@ -47873,7 +47873,7 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -47985,7 +47985,7 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
@@ -48092,7 +48092,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -48199,7 +48199,7 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
@@ -48306,7 +48306,7 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
@@ -48413,7 +48413,7 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
@@ -48520,7 +48520,7 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
@@ -48642,7 +48642,7 @@
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
@@ -48753,7 +48753,7 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
@@ -48867,7 +48867,7 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>黄高</t>
+          <t>黄阶高级</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
@@ -48974,7 +48974,7 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>黄中</t>
+          <t>黄阶中级</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
@@ -49103,7 +49103,7 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>黄中</t>
+          <t>黄阶中级</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
@@ -49333,7 +49333,7 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>黄中</t>
+          <t>黄阶中级</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
@@ -49444,7 +49444,7 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>黄中</t>
+          <t>黄阶中级</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
@@ -49551,7 +49551,7 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>黄初</t>
+          <t>黄阶初级</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
